--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487785_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487785_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>V. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0136</v>
+        <v>4.4358</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8559</v>
+        <v>3.2017</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1577</v>
+        <v>1.2341</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.3542</v>
+        <v>2.8715</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.5161</v>
+        <v>-0.9485</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1619</v>
+        <v>3.82</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.7987</v>
+        <v>3.8557</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.2095</v>
+        <v>-0.0664</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4108</v>
+        <v>3.9221</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5555</v>
+        <v>-0.9842</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3066</v>
+        <v>-0.8821</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7511</v>
+        <v>-0.102</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6244</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6384</v>
+        <v>-0.4815</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3196</v>
+        <v>-1.0348</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3188</v>
+        <v>0.5533</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1051</v>
+        <v>3.5026</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3351</v>
+        <v>3.5026</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. MORENO MARTIN</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5133</v>
+        <v>2.3981</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2792</v>
+        <v>1.3854</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2341</v>
+        <v>1.0127</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8715</v>
+        <v>-1.3542</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9485</v>
+        <v>-3.5161</v>
       </c>
       <c r="I3" t="n">
-        <v>3.82</v>
+        <v>2.1619</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8557</v>
+        <v>-0.7987</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0664</v>
+        <v>-2.2095</v>
       </c>
       <c r="L3" t="n">
-        <v>3.9221</v>
+        <v>1.4108</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9842</v>
+        <v>-0.5555</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8821</v>
+        <v>-1.3066</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.102</v>
+        <v>0.7511</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.404</v>
+        <v>1.0228</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.9573</v>
+        <v>-0.1509</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5533</v>
+        <v>1.1738</v>
       </c>
       <c r="V3" t="n">
-        <v>3.5026</v>
+        <v>2.1051</v>
       </c>
       <c r="W3" t="n">
-        <v>3.5026</v>
+        <v>2.3351</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5305</v>
+        <v>1.8361</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6839</v>
+        <v>2.5768</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1535</v>
+        <v>-0.7406</v>
       </c>
       <c r="G4" t="n">
         <v>1.6009</v>
@@ -766,13 +766,13 @@
         <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7829</v>
+        <v>0.0886</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0743</v>
+        <v>-0.0328</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7086</v>
+        <v>0.1214</v>
       </c>
       <c r="V4" t="n">
         <v>-0.4776</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5579</v>
+        <v>1.2356</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9194</v>
+        <v>1.1274</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3616</v>
+        <v>0.1082</v>
       </c>
       <c r="G5" t="n">
         <v>0.4274</v>
@@ -844,13 +844,13 @@
         <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5675</v>
+        <v>0.2453</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5773</v>
+        <v>-0.2147</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0097</v>
+        <v>0.46</v>
       </c>
       <c r="V5" t="n">
         <v>-0.4776</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1283</v>
+        <v>0.6117</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5533</v>
+        <v>-0.0653</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.425</v>
+        <v>0.677</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8703</v>
+        <v>1.8662</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5544</v>
+        <v>-0.8101</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.316</v>
+        <v>2.6762</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0156</v>
+        <v>2.1972</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0236</v>
+        <v>0.4517</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0392</v>
+        <v>1.7455</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8859</v>
+        <v>-0.331</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5308</v>
+        <v>-1.2617</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3551</v>
+        <v>0.9307</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>0.52</v>
+        <v>-0.3169</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6615</v>
+        <v>-0.7443</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1416</v>
+        <v>0.4274</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3538</v>
+        <v>-0.9376</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1238</v>
+        <v>-0.4776</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. STEVANIC</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1549</v>
+        <v>-0.2519</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0806</v>
+        <v>0.2318</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0743</v>
+        <v>-0.4837</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5937</v>
+        <v>-0.8703</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2728</v>
+        <v>-0.5544</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.321</v>
+        <v>-0.316</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0066</v>
+        <v>0.0156</v>
       </c>
       <c r="K7" t="n">
         <v>-0.0236</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0302</v>
+        <v>0.0392</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6004</v>
+        <v>-0.8859</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2492</v>
+        <v>-0.5308</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3512</v>
+        <v>-0.3551</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5845</v>
+        <v>0.1398</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7235</v>
+        <v>0.3401</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1389</v>
+        <v>-0.2003</v>
       </c>
       <c r="V7" t="n">
-        <v>0.23</v>
+        <v>-0.3538</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>-0.1238</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>V. STEVANIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2066</v>
+        <v>-0.8668</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2377</v>
+        <v>-0.6163</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0311</v>
+        <v>-0.2505</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8662</v>
+        <v>-1.5937</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8101</v>
+        <v>-0.2728</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6762</v>
+        <v>-1.321</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1972</v>
+        <v>0.0066</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4517</v>
+        <v>-0.0236</v>
       </c>
       <c r="L8" t="n">
-        <v>1.7455</v>
+        <v>0.0302</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.331</v>
+        <v>-1.6004</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2617</v>
+        <v>-0.2492</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9307</v>
+        <v>-1.3512</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1352</v>
+        <v>-0.1274</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9167</v>
+        <v>0.1877</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2185</v>
+        <v>-0.3151</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9376</v>
+        <v>0.23</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.4776</v>
+        <v>0.23</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8444</v>
+        <v>-1.2397</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0224</v>
+        <v>-0.5937</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.6459</v>
       </c>
       <c r="G9" t="n">
         <v>0.9394</v>
@@ -1156,13 +1156,13 @@
         <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1189</v>
+        <v>-0.5141</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3791</v>
+        <v>0.0496</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7398</v>
+        <v>-0.5637</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3126</v>
+        <v>-4.0443</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.339</v>
+        <v>-1.4818</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9736</v>
+        <v>-2.5625</v>
       </c>
       <c r="G10" t="n">
         <v>-3.6672</v>
@@ -1234,13 +1234,13 @@
         <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.121</v>
+        <v>-0.8527</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1091</v>
+        <v>-0.2519</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0119</v>
+        <v>-0.6008</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3975</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3722</v>
+        <v>-5.8284</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1131</v>
+        <v>-3.8335</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2592</v>
+        <v>-1.9949</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7718</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6192</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.901</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2819</v>
+        <v>0.5461</v>
       </c>
       <c r="V11" t="n">
         <v>-2.565</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.147099999999999</v>
+        <v>-1.713800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.498899999999998</v>
+        <v>1.9325</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6464</v>
+        <v>-3.6461</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5518</v>
@@ -1390,13 +1390,13 @@
         <v>12.4871</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.305</v>
+        <v>-0.8715000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.907</v>
+        <v>-2.4735</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6022</v>
+        <v>1.6021</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3714</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9426</v>
+        <v>5.4989</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3364</v>
+        <v>5.6579</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3938</v>
+        <v>-0.159</v>
       </c>
       <c r="G13" t="n">
         <v>5.6744</v>
@@ -1468,13 +1468,13 @@
         <v>0.6244</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3125</v>
+        <v>0.2438</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6524</v>
+        <v>-0.331</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3399</v>
+        <v>0.5748</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0437</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5497</v>
+        <v>3.5166</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4764</v>
+        <v>2.7169</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9267</v>
+        <v>0.7997</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2064</v>
+        <v>3.0351</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7648</v>
+        <v>0.8038</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5584</v>
+        <v>2.2313</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4313</v>
+        <v>2.7045</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3529</v>
+        <v>0.9018</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0784</v>
+        <v>1.8027</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2249</v>
+        <v>0.3306</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5881</v>
+        <v>-0.098</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6368</v>
+        <v>0.4286</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2976</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8506</v>
+        <v>0.0124</v>
       </c>
       <c r="U14" t="n">
-        <v>0.447</v>
+        <v>0.0529</v>
       </c>
       <c r="V14" t="n">
-        <v>2.9188</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>4.3163</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2563</v>
+        <v>2.9044</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7169</v>
+        <v>3.512</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5394</v>
+        <v>-0.6077</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0351</v>
+        <v>1.2064</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8038</v>
+        <v>1.7648</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2313</v>
+        <v>-0.5584</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7045</v>
+        <v>2.4313</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9018</v>
+        <v>2.3529</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8027</v>
+        <v>0.0784</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3306</v>
+        <v>-1.2249</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.098</v>
+        <v>-0.5881</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4286</v>
+        <v>-0.6368</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4162</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1951</v>
+        <v>0.6522</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0124</v>
+        <v>-0.1138</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2075</v>
+        <v>0.766</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.9188</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>4.3163</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. TREVIÑO QUINTILLÁ</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3698</v>
+        <v>1.0886</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5787</v>
+        <v>0.1795</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2089</v>
+        <v>0.9091</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.4354</v>
+        <v>-0.1306</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8655</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5699</v>
+        <v>0.507</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4671</v>
+        <v>0.1471</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2775</v>
+        <v>-0.3926</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7446</v>
+        <v>0.5396</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9025</v>
+        <v>-0.2777</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5881</v>
+        <v>-0.245</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3144</v>
+        <v>-0.0326</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4139</v>
+        <v>0.3867</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1116</v>
+        <v>0.0324</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3023</v>
+        <v>0.3543</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2737</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>P. TREVIÑO QUINTILLÁ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3132</v>
+        <v>-0.0198</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2866</v>
+        <v>0.7215</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0265</v>
+        <v>-0.7413</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1306</v>
+        <v>-1.4354</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.8655</v>
       </c>
       <c r="I17" t="n">
-        <v>0.507</v>
+        <v>-0.5699</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1471</v>
+        <v>0.4671</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3926</v>
+        <v>-0.2775</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5396</v>
+        <v>0.7446</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2777</v>
+        <v>-1.9025</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.245</v>
+        <v>-0.5881</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0326</v>
+        <v>-1.3144</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6113</v>
+        <v>1.0243</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1396</v>
+        <v>0.2544</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4717</v>
+        <v>0.7699</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2737</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2737</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5145</v>
+        <v>-0.2902</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2447</v>
+        <v>0.5525</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2698</v>
+        <v>-0.8427</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8242</v>
+        <v>-1.7536</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4094</v>
+        <v>0.5863</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4147</v>
+        <v>-2.3399</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9916</v>
+        <v>0.0999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3646</v>
+        <v>0.6967</v>
       </c>
       <c r="L18" t="n">
-        <v>0.627</v>
+        <v>-0.5968</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1674</v>
+        <v>-1.8535</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0449</v>
+        <v>-0.1105</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2123</v>
+        <v>-1.7431</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2981</v>
+        <v>-0.1204</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1957</v>
+        <v>-0.2581</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1024</v>
+        <v>0.1377</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5614</v>
+        <v>-0.4074</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5914</v>
+        <v>-0.1376</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0299</v>
+        <v>-0.2698</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0567</v>
+        <v>0.8242</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0363</v>
+        <v>0.4094</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0204</v>
+        <v>0.4147</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1915</v>
+        <v>0.9916</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0044</v>
+        <v>0.3646</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1959</v>
+        <v>0.627</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1348</v>
+        <v>-0.1674</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0407</v>
+        <v>0.0449</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1755</v>
+        <v>-0.2123</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7575</v>
+        <v>-0.191</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2577</v>
+        <v>-0.0886</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4998</v>
+        <v>-0.1024</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0466</v>
+        <v>-0.8672</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.6985</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9562</v>
+        <v>-0.1687</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7536</v>
+        <v>0.8167</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5863</v>
+        <v>0.2518</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3399</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0999</v>
+        <v>0.8944</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6967</v>
+        <v>0.403</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5968</v>
+        <v>0.4915</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8535</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1105</v>
+        <v>-0.1512</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7431</v>
+        <v>0.0735</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8768</v>
+        <v>-0.0388</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.901</v>
+        <v>-0.0747</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0242</v>
+        <v>0.0359</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1675</v>
+        <v>-1.6452</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7513</v>
+        <v>-0.4776</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>J. BERGENS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5689</v>
+        <v>-1.044</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3415</v>
+        <v>-1.4465</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2274</v>
+        <v>0.4025</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8167</v>
+        <v>0.6012</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2518</v>
+        <v>1.874</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.2728</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8944</v>
+        <v>1.2504</v>
       </c>
       <c r="K21" t="n">
-        <v>0.403</v>
+        <v>1.8864</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4915</v>
+        <v>-0.636</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.6492</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1512</v>
+        <v>-0.0124</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0735</v>
+        <v>-0.6368</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-3.3299</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7405</v>
+        <v>-0.5265</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7177</v>
+        <v>-0.7458</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0228</v>
+        <v>0.2193</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.6452</v>
+        <v>2.2112</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4776</v>
+        <v>2.2112</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6359</v>
+        <v>-1.0796</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4592</v>
+        <v>-0.6985</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8234</v>
+        <v>-0.3811</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.007</v>
+        <v>0.0567</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5203</v>
+        <v>0.0363</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4867</v>
+        <v>0.0204</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5864</v>
+        <v>0.1915</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2752</v>
+        <v>-0.0044</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3112</v>
+        <v>0.1959</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4206</v>
+        <v>-0.1348</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.245</v>
+        <v>0.0407</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1755</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2081</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4554</v>
+        <v>0.2393</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1272</v>
+        <v>0.1505</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3282</v>
+        <v>0.0888</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7076</v>
+        <v>-1.1675</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.7076</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BERGENS</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8836</v>
+        <v>-1.7915</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8751</v>
+        <v>-2.6736</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.8821</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6012</v>
+        <v>-3.007</v>
       </c>
       <c r="H23" t="n">
-        <v>1.874</v>
+        <v>-1.5203</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2728</v>
+        <v>-1.4867</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2504</v>
+        <v>-2.5864</v>
       </c>
       <c r="K23" t="n">
-        <v>1.8864</v>
+        <v>-1.2752</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.636</v>
+        <v>-1.3112</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6492</v>
+        <v>-0.4206</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0124</v>
+        <v>-0.245</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6368</v>
+        <v>-0.1755</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.3299</v>
+        <v>0.2081</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.1624</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3661</v>
+        <v>0.2998</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1744</v>
+        <v>-0.0871</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1918</v>
+        <v>0.3869</v>
       </c>
       <c r="V23" t="n">
-        <v>2.2112</v>
+        <v>0.7076</v>
       </c>
       <c r="W23" t="n">
-        <v>2.2112</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0733</v>
+        <v>-4.6471</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1466</v>
+        <v>-4.0395</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9267</v>
+        <v>-0.6077</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3361</v>
@@ -2326,13 +2326,13 @@
         <v>1.2487</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4417</v>
+        <v>-0.0155</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.46</v>
+        <v>-0.3528</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0183</v>
+        <v>0.3374</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5036</v>
@@ -2359,37 +2359,37 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.147400000000003</v>
+        <v>2.8617</v>
       </c>
       <c r="E25" t="n">
-        <v>3.6461</v>
+        <v>3.646100000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4988</v>
+        <v>-0.7846</v>
       </c>
       <c r="G25" t="n">
-        <v>2.552000000000001</v>
+        <v>2.552</v>
       </c>
       <c r="H25" t="n">
-        <v>4.327800000000001</v>
+        <v>4.327799999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7758</v>
+        <v>-1.775800000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>9.350499999999997</v>
+        <v>9.3505</v>
       </c>
       <c r="K25" t="n">
         <v>7.064599999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>2.285899999999999</v>
+        <v>2.2859</v>
       </c>
       <c r="M25" t="n">
         <v>-6.798500000000002</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.736800000000001</v>
+        <v>-2.7368</v>
       </c>
       <c r="O25" t="n">
         <v>-4.0616</v>
@@ -2404,22 +2404,22 @@
         <v>10.4059</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3049</v>
+        <v>2.0191</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.6021</v>
+        <v>-1.6022</v>
       </c>
       <c r="U25" t="n">
-        <v>2.906899999999999</v>
+        <v>3.621500000000001</v>
       </c>
       <c r="V25" t="n">
         <v>0.3713999999999997</v>
       </c>
       <c r="W25" t="n">
-        <v>8.385000000000002</v>
+        <v>8.385</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.013500000000001</v>
+        <v>-8.013499999999999</v>
       </c>
     </row>
   </sheetData>
